--- a/outputs/metrics/threshold_recommendations_from_validation.xlsx
+++ b/outputs/metrics/threshold_recommendations_from_validation.xlsx
@@ -480,31 +480,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6110236220472441</v>
+        <v>0.614853195164076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4399092970521542</v>
+        <v>0.4438902743142145</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5014836795252225</v>
+        <v>0.4889589905362776</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6075949367088608</v>
+        <v>0.6078799249530957</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7068723702664796</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -519,31 +519,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6232394366197183</v>
+        <v>0.6275862068965518</v>
       </c>
       <c r="D3" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4526854219948849</v>
+        <v>0.457286432160804</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4893617021276596</v>
+        <v>0.4826498422712934</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6165137614678899</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7068723702664796</v>
+        <v>0.7124824684431977</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -558,31 +558,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6178861788617886</v>
+        <v>0.616695059625213</v>
       </c>
       <c r="D4" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4470588235294118</v>
+        <v>0.4458128078817734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8796296296296297</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5015197568389058</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6178861788617886</v>
+        <v>0.6018348623853211</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6704067321178121</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
